--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N111_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N111_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.54915828241184</v>
+        <v>5.289238220891924</v>
       </c>
       <c r="D2" t="n">
-        <v>10.75059264090572</v>
+        <v>1.74697130414718</v>
       </c>
       <c r="E2" t="n">
-        <v>9.649872173708726</v>
+        <v>1.568104228227668</v>
       </c>
       <c r="F2" t="n">
-        <v>5.271349366268306</v>
+        <v>0.8565942720185999</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.14464327249656</v>
+        <v>3.923504531780691</v>
       </c>
       <c r="D3" t="n">
-        <v>12.93326969014777</v>
+        <v>2.101656324649013</v>
       </c>
       <c r="E3" t="n">
-        <v>9.649872173708726</v>
+        <v>1.568104228227668</v>
       </c>
       <c r="F3" t="n">
-        <v>5.271349366268306</v>
+        <v>0.8565942720185999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.21412147213077</v>
+        <v>1.49729473922125</v>
       </c>
       <c r="D4" t="n">
-        <v>22.8632286984714</v>
+        <v>3.715274663501602</v>
       </c>
       <c r="E4" t="n">
-        <v>9.649872173708726</v>
+        <v>1.568104228227668</v>
       </c>
       <c r="F4" t="n">
-        <v>5.271349366268306</v>
+        <v>0.8565942720185999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
